--- a/5/search/FY2_Missile3_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY2_Missile3_results/fine_tuned/comparison.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274</v>
+        <v>268.4</v>
       </c>
       <c r="C3" t="n">
-        <v>137.7</v>
+        <v>137.66</v>
       </c>
       <c r="D3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>3.800000000000001</v>
+        <v>3.700000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY2_Missile3_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY2_Missile3_results/fine_tuned/comparison.xlsx
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>270</v>
+        <v>238.5</v>
       </c>
       <c r="C2" t="n">
-        <v>137.2</v>
+        <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>3.700000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>268.4</v>
+        <v>270.8</v>
       </c>
       <c r="C3" t="n">
-        <v>137.66</v>
+        <v>139</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>3.700000000000003</v>
+        <v>3.800000000000001</v>
       </c>
     </row>
   </sheetData>
